--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92570593407</v>
+        <v>46157.93105831715</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93105831715</v>
+        <v>46157.93176880923</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93176880923</v>
+        <v>46157.93402010549</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402010549</v>
+        <v>46157.93720082245</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720082245</v>
+        <v>46158.28218084382</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218084382</v>
+        <v>46158.29689904861</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29689904861</v>
+        <v>46158.29817157853</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29817157853</v>
+        <v>46158.33389205949</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389205949</v>
+        <v>46158.36858974632</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2025 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36858974632</v>
+        <v>46158.3728965466</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
